--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R58-AutreTypeDiplome.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R58-AutreTypeDiplome.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,7 +505,7 @@
     <t>DIP322</t>
   </si>
   <si>
-    <t>Master en Psychologie ou Psychanalyse</t>
+    <t>Master en Psychologie ou Psychanalyse + formation établissement agréé incluant un stage en ESSMS</t>
   </si>
   <si>
     <t>Article 52 de la Loi n° 2004-806 du 9 août 2004 relative à la politique de santé publique ; article 1 du Décret n° 2010-534 du 20 mai 2010 relatif à l'usage du titre de psychothérapeute</t>
